--- a/data/trans_bre/IP07_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>-3,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>-48,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,18</t>
+          <t>-6,0; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,62</t>
+          <t>-6,99; 2,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 7,19</t>
+          <t>-3,94; 7,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 34,64</t>
+          <t>-12,34; 3,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 150,76</t>
+          <t>-73,61; 193,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,9; 295,67</t>
+          <t>-88,49; 215,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,72; 2054,72</t>
+          <t>-100,0; 148,75</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,25</t>
+          <t>-3,25; 0,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,11</t>
+          <t>-1,53; 1,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,37</t>
+          <t>-1,78; 1,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,49</t>
+          <t>-0,53; 2,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,09; -2,22</t>
+          <t>-80,29; 4,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 117,85</t>
+          <t>-46,18; 103,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,04; 87,08</t>
+          <t>-56,7; 91,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 251,42</t>
+          <t>-27,33; 275,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-43,22%</t>
+          <t>-42,15%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; -0,89</t>
+          <t>-5,32; -0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,51</t>
+          <t>-2,45; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,67</t>
+          <t>-2,64; 0,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,7</t>
+          <t>-5,0; 1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,12</t>
+          <t>-100,0; 73,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,81</t>
+          <t>-100,0; 188,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,48</t>
+          <t>-3,3; -0,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,1</t>
+          <t>-1,47; 1,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,07</t>
+          <t>-1,38; 1,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,05</t>
+          <t>-1,48; 1,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,66; -13,92</t>
+          <t>-74,76; -18,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 60,36</t>
+          <t>-47,95; 64,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 74,47</t>
+          <t>-51,57; 70,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 191,18</t>
+          <t>-48,88; 97,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-11,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-40,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-48,14%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.6251470830980287</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.75120050468262</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7680738858603243</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.612438034317087</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1120206982621552</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4029067212613522</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2608371361407755</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.4813804646850942</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 4,56</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,99; 2,36</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; 7,39</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-12,34; 3,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-73,61; 193,01</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-88,49; 215,81</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 148,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.9957201593414</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.987606460727602</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.941746540324381</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.34083002085426</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7360517703335742</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8848645755233651</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.563866321131809</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.364820071242907</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.393449561027612</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.507262267471477</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.930124181515583</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.158095214349073</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>1.487528687596424</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-53,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-7,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,25; 0,04</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,53; 1,93</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,78; 1,31</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 2,74</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-80,29; 4,69</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-46,18; 103,35</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-56,7; 91,72</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-27,33; 275,75</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.802425738073012</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2105031011747249</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.179875883577724</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.084772887500097</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.5353301025416112</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.0809974659313616</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.0769390720574739</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.6781269757889538</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,55</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-87,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-27,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-44,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-42,15%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.249137147193685</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.530276294131869</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.781627009344903</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-0.5321782642932782</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8028575214117272</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4618218846411695</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5670348756403941</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2732508691908026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; -0,8</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 1,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,64; 0,63</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,0; 1,69</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 73,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 188,88</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04398066484639084</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.933911718486901</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.314923123142886</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.741719931452143</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.04692737596367809</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.03345695977336</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.9171787703131463</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.757518669915315</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +817,189 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-51,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-8,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.553981487315279</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3618252327584189</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4997544180409078</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.317437294612039</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.8755020110692805</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2782488458698896</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4440159512661098</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.4214975471197017</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; -0,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,47; 1,18</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,38; 1,02</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,48; 1,67</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-74,76; -18,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-47,95; 64,15</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-51,57; 70,58</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-48,88; 97,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.320184445578255</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.447535929737921</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.636040128508063</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.003692187692945</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.797151385948261</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.493885826169913</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6282661272605323</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.687460739101208</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.7312566054455488</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>1.888818166652301</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.823885407510627</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1559636663731548</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.1740796697692185</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.1209422311480572</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5161264129252142</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06239877526168341</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.08334277861835468</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.04947824029016718</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.303265067499479</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.470727611263813</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.379536634705319</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.480884812625353</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7476248685406128</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.47951565071138</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5157241096654185</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4887537677625639</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.6068988213794948</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.180919500150836</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.021592243925387</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.671419149910535</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.1860170913690972</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6415361890381077</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7057769517258944</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.9712835615935693</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1007,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
